--- a/summer_camp_surveys/043_summer_camp_survey_form_for_parents--summer_camp_surveys.xlsx
+++ b/summer_camp_surveys/043_summer_camp_survey_form_for_parents--summer_camp_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_description</t>
+          <t>summer_camp_survey_form_for_parents_description_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_description</t>
+          <t>summer_camp_survey_form_for_parents_description_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Summer Camp Survey Form For Parents Description 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_category</t>
+          <t>summer_camp_survey_form_for_parents_category_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Summer Camp Survey Form For Parents Category 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How often do you get updates about your child?</t>
+          <t>Summer Camp Survey Form For Parents Improve Frequency</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve</t>
+          <t>summer_camp_survey_form_for_parents_improve_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve_frequency</t>
+          <t>summer_camp_survey_form_for_parents_improve_frequency_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_category_choices</t>
+          <t>summer_camp_survey_form_for_parents_category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_category_choices</t>
+          <t>summer_camp_survey_form_for_parents_category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve_frequency_choices</t>
+          <t>summer_camp_survey_form_for_parents_improve_frequency_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve_frequency_choices</t>
+          <t>summer_camp_survey_form_for_parents_improve_frequency_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve_frequency_choices</t>
+          <t>summer_camp_survey_form_for_parents_improve_frequency_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>summer_camp_survey_form_for_parents_improve_frequency_choices</t>
+          <t>summer_camp_survey_form_for_parents_improve_frequency_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
